--- a/www/download/COUNTRY.ITA.EXI382.xlsx
+++ b/www/download/COUNTRY.ITA.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>Itália</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -967,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1312</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1312</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1312</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1312</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1312</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1312</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1312</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1312</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1312</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1312</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1312</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1312</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1312</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1312</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1312</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1312</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1312</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1312</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1312</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1312</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1312</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1312</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1312</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1312</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1312</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1312</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1312</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>24.19</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>20.585</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>20.706</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>20.809</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>20.973</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>21.209</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>21.525</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>21.955</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>22.358</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>22.652</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>23.021</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>23.175</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>23.594</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>23.799</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>23.369</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>23.002</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>22.859</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>22.951</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>22.886</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>22.199</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>22.264</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>22.498</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>22.65</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>22.987</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>23.909</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>23.476</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>23.886</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>18.654</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>14.66</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>14.75</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>14.87</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>15.01</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>15.255</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>15.505</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>15.872</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>16.265</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>16.512</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>16.605</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>17.026</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>17.403</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>17.626</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>17.412</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>17.254</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>17.097</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>17.225</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>17.201</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>16.717</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>16.841</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>17.05</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>17.177</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>17.398</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>18.274</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>17.825</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>18.297</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>44239.139</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>42277.24</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>41883.317</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>42668.851</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>43000.464</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>43355.111</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>43933.948</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>44982.249</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>41719.222</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>46023.217</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>46274.049</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>46083.019</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>46725.658</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>47175.487</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>45906.791</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>44663.348</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>44485.91</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>44335.815</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>43414.7</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>41989.162</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>41919.036</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>42262.971</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>42506.737</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>43062.898</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>44490.936</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>43708.756</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>44236.891</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>32965.059</t>
+          <t>91731380591.5918</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>15256.702</t>
+          <t>87227109105.4477</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>14869.773</t>
+          <t>87325856544.0257</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>15366.869</t>
+          <t>87248229854.8415</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>15468.39</t>
+          <t>92143536276.4102</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>16111.105</t>
+          <t>92630013850.0625</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>16412.412</t>
+          <t>94498057324.0102</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>16907.525</t>
+          <t>94175846173.1156</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>15749.482</t>
+          <t>85194424535.2055</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>18018.585</t>
+          <t>101462361105.428</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>17606.361</t>
+          <t>102284766996.96</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>18786.101</t>
+          <t>107389583054.926</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>33100.231</t>
+          <t>100259419703.289</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>33466.172</t>
+          <t>107605573013.721</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>19689.855</t>
+          <t>94104295885.0435</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>19558.874</t>
+          <t>95782825086.4154</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>19384.964</t>
+          <t>99505136377.7639</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>19582.351</t>
+          <t>94987246043.4518</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>19397.416</t>
+          <t>93634828891.4925</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>30475.362</t>
+          <t>78358708130.4546</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>30586.541</t>
+          <t>74286757805.8834</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>30921.886</t>
+          <t>76898275413.1723</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>31156.588</t>
+          <t>72436811063.7545</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>31482.167</t>
+          <t>77395274506.5732</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>32850.18</t>
+          <t>76509440038.4363</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>32037.56</t>
+          <t>77366771722.516</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>32735.886</t>
+          <t>79171900172.7954</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>30486604386.5262</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>31061539684.1251</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>26717419800.762</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>25906966831.2065</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>31053112032.87</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>31375106425.9737</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>29545314053.6766</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>29554916577.7859</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>29544239760.7449</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>32265939601.0886</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>31749945332.7764</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>31685932194.084</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>28168333791.0576</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>28438337195.2406</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>27563485880.8435</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>28547587269.4145</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>27082040970.5207</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>25944107304.8473</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>25801789535.2421</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>22706892295.9782</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>21179382192.3163</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>21501576754.5047</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>20869065991.648</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>22366149550.3354</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>21018650297.171</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>22530585878.8392</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>22265433076.0142</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2704711938.70318</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>8516690.91166826</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>8913503.82090399</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>11333020.9933979</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>8843665.40360386</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>6976333.84561674</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>221110787.726292</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>6960344.17213837</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>5737220.66486847</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>7035491.46122318</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>6595613.73496293</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>10144439.1906972</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>5956747.89116383</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>6136315.06165209</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>6112504.40168858</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>5553772.13301866</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>6072059.33475177</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>8508176.45940566</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>5532005.88968654</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1658200678.67472</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>1704854198.2785</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>1754173728.6213</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>904846096.251853</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>871483767.682474</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>908361933.120511</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>933666608.020214</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>957176218.371187</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>74575.0697740805</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>186876.363125371</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>197937.34864394</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>207053.684507896</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>220451.981438914</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>261492.402670317</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>263446.191091022</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>266556.003061537</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>219606.591599927</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>237226.763577035</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>253811.298418853</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>269315.953519416</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>280248.020658488</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>282832.30751102</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>274242.400799515</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>306212.703940804</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>315442.465204416</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>346526.850723125</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>328429.652093342</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>328744.802729989</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>361969.42117211</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>329338.42814978</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>346463.463418319</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>341890.56398929</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>370478.520933191</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>341000.865446222</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>334336.83900087</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>341938.136605008</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>662845.119919313</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>722763.281738959</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>742390.042011105</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>827015.406279699</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>993810.14027472</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1018004.08708763</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>983444.148410948</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>817251.503951286</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>951150.968657795</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>1027938.56454156</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>1154471.2980225</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>1116680.60879583</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>1204268.79572171</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1055393.70950339</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1238793.73337053</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>1339768.07932861</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1411638.62498508</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>1359294.86798568</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>1177436.66340236</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>1260954.35746914</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>1189726.88270848</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>1184855.48488958</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>1231239.21818013</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>1296825.11876309</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>1247497.18536102</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>1253343.44595011</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0.0812965052547474</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-0.508823382383978</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-0.443442775878555</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-0.406844147363063</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-0.50187311392108</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-0.48650038724113</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-0.444500337001758</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-0.427928515531484</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>-0.466918691171692</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-0.441560195588257</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>-0.44546799008742</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-0.407115407401149</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.175086579332006</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.176797777248663</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>-0.285654394908025</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>-0.314867704390882</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>-0.284213327160273</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>-0.245210067554328</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>-0.248214315774786</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.34211947176898</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>0.444165880536186</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>0.438121792635272</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>0.49295556126346</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>0.407580996389107</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>0.562906272658126</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>0.42195860454846</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>0.470255956627585</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1634.34070650618</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2118.75198216427</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1811.31365468915</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1742.27731957901</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2068.89716731858</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2056.70969688501</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1905.58376570014</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1862.03199124075</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1816.40802208097</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1954.13767297514</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1912.08289919041</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1861.01021919658</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1618.54418887409</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>1613.41282835997</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1583.05301527925</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1654.54893180813</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1584.01371990113</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1506.16287117468</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>1499.99067135806</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>1358.34650869179</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>1257.6094393685</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>1261.07728453266</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>1214.90881003045</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>1285.57726224104</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>1150.22358383898</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>1264.00298026839</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>1216.89170494054</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.483</t>
+          <t>60254363449.8688</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.559</t>
+          <t>40893514080.6829</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.593</t>
+          <t>34311640366.7612</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.564</t>
+          <t>35643114572.2231</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.629</t>
+          <t>36045858932.8658</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>35541408524.8895</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.697</t>
+          <t>35550997680.7774</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>33380500459.4122</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>33882598854.1187</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.774</t>
+          <t>38308061114.7294</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.795</t>
+          <t>36675581103.9793</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.824</t>
+          <t>34912419966.5793</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.859</t>
+          <t>30697431389.5646</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.858</t>
+          <t>31576559020.9658</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.834</t>
+          <t>26721367600.0673</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>24662304387.2609</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>26490650080.9793</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.862</t>
+          <t>28537826761.0505</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.852</t>
+          <t>30999944478.8919</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.878</t>
+          <t>26483404698.4384</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.893</t>
+          <t>24234480726.0847</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.894</t>
+          <t>27900666902.236</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0.938</t>
+          <t>24161398460.531</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.948</t>
+          <t>25122620729.1065</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>23937887780.4509</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.963</t>
+          <t>27070313687.3937</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>0.978</t>
+          <t>27861172427.6319</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>51523940798.7864</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>36239288581.4887</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>30280023029.681</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>31872492654.4528</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>32362378250.6874</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>32537387791.4162</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>31767321717.4519</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>30615998187.6545</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>30516545468.6864</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>33751140359.9319</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>33043998882.696</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>32194290415.7181</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>28973419632.3332</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>29372679524.2081</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>25473649604.3124</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>23365277492.194</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>23558395695.3667</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>26368535474.4081</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>28679882589.9645</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>23895179094.399</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>22064569858.2679</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>25540705987.54</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>25308943708.8118</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>26539836502.4629</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>25297925519.5664</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>28517536240.94</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>28696371755.3693</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>8730422651.08246</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>4654225499.19422</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>4031617337.08021</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>3770621917.7703</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>3683480682.17846</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>3004020733.47326</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3783675963.32549</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2764502271.75775</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>3366053385.43223</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>4556920754.79752</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>3631582221.28329</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2718129550.86118</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>1724011757.23142</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2203879496.75772</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1247717995.75496</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>1297026895.06686</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>2932254385.61258</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>2169291286.64238</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>2320061888.92741</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2588225604.0394</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>2169910867.81679</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>2359960914.69602</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>-1147545248.28084</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>-1417215773.3564</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>-1360037739.11548</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>-1447222553.54632</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>-835199327.737415</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.687</t>
+          <t>1767.2068943407</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.928</t>
+          <t>1040.68143216669</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2.045</t>
+          <t>1008.09969966707</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2.102</t>
+          <t>1033.44198902488</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2.225</t>
+          <t>1030.5733035739</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2.448</t>
+          <t>1056.11963290787</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2.578</t>
+          <t>1058.55113966135</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2.658</t>
+          <t>1065.21540535696</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2.738</t>
+          <t>968.293165777163</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>1091.26825988985</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2.958</t>
+          <t>1060.31117320753</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>3.125</t>
+          <t>1103.36428563066</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>3.251</t>
+          <t>1901.92955440176</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>3.322</t>
+          <t>1898.66063019849</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>1130.84696409233</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>3.204</t>
+          <t>1133.58490784732</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>3.292</t>
+          <t>1133.81591030051</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>3.225</t>
+          <t>1136.83657178612</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>1127.67151319835</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>3.193</t>
+          <t>1823.06329872467</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>3.258</t>
+          <t>1816.19664337623</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>3.357</t>
+          <t>1813.58272508372</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>3.454</t>
+          <t>1813.80486436293</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>3.562</t>
+          <t>1809.55412372043</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>3.581</t>
+          <t>1797.69165414125</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>3.621</t>
+          <t>1797.35991396754</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>3.645</t>
+          <t>1789.14227775953</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.483</t>
+          <t>1828.81315316155</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.559</t>
+          <t>2053.74877340241</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.593</t>
+          <t>2022.80141604198</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.564</t>
+          <t>2050.48997794285</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.629</t>
+          <t>2050.2283357572</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>2044.13640114148</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.697</t>
+          <t>2041.06610917492</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>2048.83848781537</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>1865.98064210257</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.774</t>
+          <t>2031.77761492515</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.795</t>
+          <t>2010.07988358413</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.824</t>
+          <t>1988.46262383934</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.859</t>
+          <t>1980.37068117971</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.858</t>
+          <t>1982.26326537471</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.834</t>
+          <t>1964.45634545311</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1941.73273396006</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>1946.06638844394</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.862</t>
+          <t>1931.72595135731</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.852</t>
+          <t>1897.0064537548</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.878</t>
+          <t>1891.50457987421</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0.893</t>
+          <t>1882.80367367008</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0.894</t>
+          <t>1878.48184881182</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>0.938</t>
+          <t>1876.71755864774</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>0.948</t>
+          <t>1873.35825301801</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1860.87909358369</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.963</t>
+          <t>1861.83017286028</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>0.978</t>
+          <t>1852.03643675614</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>257538.322058722</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>288656.210549304</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>313722.477411303</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>322201.481987153</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>321716.517807958</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>378228.820684606</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>400479.577960579</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>389879.538466302</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>377790.898380795</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>400114.494711428</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>421505.631076587</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>463088.433006473</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>496100.396568251</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>486805.953834717</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>397876.118392834</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>455776.883453784</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>498956.84787546</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>535427.966825001</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>534636.568112945</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>546889.844119926</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>577587.793479983</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>583579.65236962</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>625057.157711373</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>647411.543929984</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>658226.830981961</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>682067.927932159</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>707328.036071517</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>15046651537.277</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>14327006678.0997</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>14765970608.8041</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>14785229296.4953</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>14244281453.234</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>15733376540.1302</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>16172918435.5486</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>15360543275.2859</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>13800649325.8924</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>16466611197.042</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>16609433844.5656</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>18420802873.5188</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>17958659602.087</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>18993591530.5998</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>14754521012.4897</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>15800281603.4313</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>17405437847.2694</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>18260635023.689</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>18471298067.4492</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>15626139944.7883</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>14805043957.1885</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>15074954618.204</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>15511707595.384</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16896360147.2794</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>16928455165.2952</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>17542851297.7176</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>18031385153.4652</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>214539.357524833</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>227398.258165835</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>260562.385968496</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>277255.300218512</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>294356.214626295</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>364461.810579605</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>378949.581339717</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>376572.876197362</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>369499.570305132</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>388939.49542617</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>423435.585837293</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>479751.518040299</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>503259.044789308</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>503176.178135015</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>410624.602748421</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>494899.416630383</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>529121.212038952</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>511975.568942408</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>484045.838811839</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>485335.955724353</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>512358.595667188</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>510694.219494202</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>560019.648665048</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>592038.580471622</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>586794.910737665</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>607525.920952427</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>632303.383711535</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>44239.139</t>
+          <t>50940973298.8371</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>42277.24</t>
+          <t>42776699837.0856</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>41883.317</t>
+          <t>39126694812.9539</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>42668.851</t>
+          <t>41960558709.4274</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>43000.464</t>
+          <t>45271059860.7277</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>43355.111</t>
+          <t>49138963154.7531</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>43933.948</t>
+          <t>48251580037.6532</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>44982.249</t>
+          <t>46514392688.6311</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>41719.222</t>
+          <t>46274736792.3239</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>46023.217</t>
+          <t>52725290962.4127</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>46274.049</t>
+          <t>53607801009.9778</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>46083.019</t>
+          <t>55812551582.762</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>46725.658</t>
+          <t>49545069137.2621</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>47175.487</t>
+          <t>52813515439.9824</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>45906.791</t>
+          <t>43352356000.0194</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>44663.348</t>
+          <t>45286473217.4462</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>44485.91</t>
+          <t>47374514365.1165</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>44335.815</t>
+          <t>44241417960.9182</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>43414.7</t>
+          <t>43675894563.3852</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>41989.162</t>
+          <t>35565991287.1544</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>41919.036</t>
+          <t>32734151882.2791</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>42262.971</t>
+          <t>35245645295.2306</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>42506.737</t>
+          <t>33408513874.6606</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>43062.898</t>
+          <t>36515478309.3333</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>44490.936</t>
+          <t>34346936872.4805</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>43708.756</t>
+          <t>37379509753.2552</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>44236.891</t>
+          <t>38582525027.6341</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>32965.059</t>
+          <t>42998.9645338893</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>15256.702</t>
+          <t>61257.9523834692</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>14869.773</t>
+          <t>53160.091442807</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>15366.869</t>
+          <t>44946.1817686412</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>15468.39</t>
+          <t>27360.303181663</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>16111.105</t>
+          <t>13767.0101050008</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>16412.412</t>
+          <t>21529.9966208614</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>16907.525</t>
+          <t>13306.6622689403</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>15749.482</t>
+          <t>8291.32807566261</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>18018.585</t>
+          <t>11174.9992852579</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>17606.361</t>
+          <t>-1929.95476070595</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>18786.101</t>
+          <t>-16663.0850338256</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>33100.231</t>
+          <t>-7158.64822105777</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>33466.172</t>
+          <t>-16370.224300298</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>19689.855</t>
+          <t>-12748.4843555872</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>19558.874</t>
+          <t>-39122.5331765997</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>19384.964</t>
+          <t>-30164.3641634912</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>19582.351</t>
+          <t>23452.3978825925</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>19397.416</t>
+          <t>50590.7293011057</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>30475.362</t>
+          <t>61553.8883955724</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>30586.541</t>
+          <t>65229.1978127949</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>30921.886</t>
+          <t>72885.4328754178</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>31156.588</t>
+          <t>65037.5090463247</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>31482.167</t>
+          <t>55372.963458362</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>32850.18</t>
+          <t>71431.9202442956</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>32037.56</t>
+          <t>74542.0069797315</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>32735.886</t>
+          <t>75024.6523599819</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>61605.853</t>
+          <t>-35894321761.56</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>62804.581</t>
+          <t>-28449693158.9859</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>63342.402</t>
+          <t>-24360724204.1498</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>63280.089</t>
+          <t>-27175329412.9321</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>66280.083</t>
+          <t>-31026778407.4937</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>66310.221</t>
+          <t>-33405586614.6229</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>67583.399</t>
+          <t>-32078661602.1047</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>67773.208</t>
+          <t>-31153849413.3452</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>61423.667</t>
+          <t>-32474087466.4315</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>72600.968</t>
+          <t>-36258679765.3706</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>73171.918</t>
+          <t>-36998367165.4122</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>76129.163</t>
+          <t>-37391748709.2432</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>72038.524</t>
+          <t>-31586409535.1751</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>76548.237</t>
+          <t>-33819923909.3827</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>67812.801</t>
+          <t>-28597834987.5297</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>68134.428</t>
+          <t>-29486191614.0149</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>70226.364</t>
+          <t>-29969076517.8471</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>67507.65</t>
+          <t>-25980782937.2292</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>66305.628</t>
+          <t>-25204596495.936</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>56089.603</t>
+          <t>-19939851342.3661</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>53353.402</t>
+          <t>-17929107925.0906</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>54898.081</t>
+          <t>-20170690677.0266</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>52448.308</t>
+          <t>-17896806279.2766</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>55538.749</t>
+          <t>-19619118162.0538</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>55038.861</t>
+          <t>-17418481707.1852</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>55406.31</t>
+          <t>-19836658455.5376</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>56276.203</t>
+          <t>-20551139874.1689</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>361560.300766828</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.407</t>
+          <t>415455.008601657</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.449</t>
+          <t>443383.551159409</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.466</t>
+          <t>450970.786729012</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.516</t>
+          <t>468245.447084373</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.617</t>
+          <t>495890.844471272</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.633</t>
+          <t>513131.69707078</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.616</t>
+          <t>527175.080469845</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.514</t>
+          <t>552327.015879517</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.596</t>
+          <t>562117.928145589</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.642</t>
+          <t>571016.422058947</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.716</t>
+          <t>599610.761800948</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.699</t>
+          <t>623101.093750574</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.753</t>
+          <t>624255.445747331</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.664</t>
+          <t>597766.524382997</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.768</t>
+          <t>626312.02538051</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.825</t>
+          <t>628970.384194731</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.875</t>
+          <t>608188.92200916</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.836</t>
+          <t>600474.887337607</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.726</t>
+          <t>607031.920517272</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0.771</t>
+          <t>618705.744907712</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>629543.905163345</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>0.722</t>
+          <t>657490.323747663</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.743</t>
+          <t>675892.981314941</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.779</t>
+          <t>681606.865951</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>0.747</t>
+          <t>687044.509534453</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>0.744</t>
+          <t>686447.123101861</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>20006.175</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>24591.997</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>23915.228</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>24333.661</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>24562.088</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>24372.91</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>24454.866</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>25525.737</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>22892.9</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>25305.749</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>25255.429</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>25051.925</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>25161.63</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>25272.043</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>24452.854</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>23676.192</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>23428.044</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>23317.321</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>22623.829</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>21878.05</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>21324.749</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>21286.866</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>21181.24</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>21491.123</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>21857.307</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>21148.053</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>21119.577</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>546801.43253196</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>632303.995894648</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>671341.131656272</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>637737.96833091</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>711245.695197224</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>754872.652042531</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>788619.080642554</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>813961.707932353</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>848816.529147626</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>875707.245197116</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>898937.325501687</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>931846.391821226</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.244</t>
+          <t>971156.693182024</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>970849.749523291</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>943160.820550274</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.267</t>
+          <t>984567.178093875</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>995500.457439242</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.302</t>
+          <t>974756.007959492</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>964172.877176838</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.283</t>
+          <t>992940.655803307</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>1009962.02796404</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>1011348.83164114</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>1060781.21360317</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0.287</t>
+          <t>1071965.50865707</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.309</t>
+          <t>1097190.0803111</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>1089903.52770173</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>1105918.36035345</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>25954.59</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>27016.58</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>23171.158</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>22484.522</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>26763.242</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>27452.199</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>25650.581</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>25909.839</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>26222.597</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>28326.072</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>28008.571</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>27719.397</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>24928.673</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>24876.808</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>24215.901</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>24983.284</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>23683.368</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>22496.815</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>22294.838</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>20043.579</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>18705.324</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>18994.939</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>18581.411</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>19747.7</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>18608.718</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>19893.002</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>19580.417</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>27.01</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>-43.53</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>-35.83</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>-31.66</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>-42.2</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>-41.31</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>-36.02</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>-34.74</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>-39.94</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>-36.39</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>-37.14</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>-32.23</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>32.78</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>34.53</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>-18.69</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>-21.71</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>-18.15</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>-12.96</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>-13</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>52.05</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>63.52</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>62.79</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>67.68</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>59.42</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>76.53</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>61.05</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>67.19</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>3057.076</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>8.183</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>8.651</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>11.362</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>8.424</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>6.608</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>248.822</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>6.637</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>5.456</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>6.658</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>6.184</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>10.166</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>5.633</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>5.731</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>5.692</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>5.134</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>5.636</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>8.398</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>1874.653</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>1927.615</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>1983.376</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>1022.753</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>985.012</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>1026.673</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>1055.343</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>1081.823</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>364267.52378389</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>418422.110827416</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>440568.467631156</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>488911.340096616</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>478202.767125294</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>502354.818907864</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>540137.519414804</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>553567.758039416</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>566839.467729922</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>601277.493070702</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>621206.315348196</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>643450.753310067</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>671499.662443196</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>689118.221495855</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>656565.796827052</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>659539.237029472</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>688875.55725322</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>681667.79125081</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>679548.342185263</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>652071.971189617</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>662503.07255064</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>710812.420274505</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>689158.58903681</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>727261.805013095</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>707234.950242242</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>738542.119244423</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>720050.566731884</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>32965058780.2349</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>15256701999.9944</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>14869772999.9994</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>15366869000.0011</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>15468389999.9934</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>16111105000.0058</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>16412411999.9946</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>16907524999.9971</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>15749481999.9952</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>18018584999.993</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>17606360999.999</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>18786101000.0043</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>33100231000.0161</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>33466172000.0071</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>19689854999.9952</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>19558873999.9956</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>19384963999.9982</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>19582350999.989</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>19397415999.9869</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>30475362293.7934</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>30586541132.9788</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>30921886106.6731</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>31156588130.605</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>31482167069.4489</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>32850180392.2562</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>32037560455.9335</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>32735885606.9028</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>44239138748.0209</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>42277239999.999</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>41883316999.9999</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>42668851000.0019</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>43000463999.9966</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>43355111000.0039</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>43933947999.9914</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>44982249000.0018</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>41719221999.9942</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>46023216999.9928</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>46274049000.0006</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>46083018999.9993</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>46725658000.0113</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>47175487000.0046</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>45906790999.9975</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>44663348000.0014</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>44485909999.9937</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>44335814999.9857</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>43414699999.9994</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>41989161562.2158</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>41919035992.4415</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>42262970778.6776</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>42506737458.1</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>43062898006.7977</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>44490936433.3799</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>43708756362.2667</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>44236891369.6456</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>20006174730.9367</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>24591996570.1042</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>23915227778.0326</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>24333660792.7811</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>24562087954.6869</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>24372909773.6332</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>24454865735.1004</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>25525737461.9652</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>22892900294.5082</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>25305748869.5939</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>25255429084.467</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>25051924641.2016</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>25161629657.4847</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>25272042773.7043</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>24452853751.8059</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>23676191661.8669</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>23428044005.372</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>23317321195.1803</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>22623828722.4789</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>21878049874.9597</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>21324748643.3357</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>21286866355.7034</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>21181240041.6626</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>21491123463.6185</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>21857306565.6703</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>21148052615.865</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>21119576543.0431</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>24190081.2401435</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>20585400.0000005</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>20705600.0000005</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>20809099.9999958</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>20973499.9999966</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>21209499.999997</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>21525000.0000006</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>21955000.0000076</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>22357799.9999964</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>22651699.9999964</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>23021000.0000051</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>23175199.9999989</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>23594399.9999922</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>23798800.0000025</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>23368700.0000038</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>23001799.9999995</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>22859399.9999991</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>22951400.0000018</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>22885900.0000066</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>22198815.6988804</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>22264156.6822155</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>22498471.7341877</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>22649512.3159225</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>22987006.3226949</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>23908558.3726447</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>23476231.6130682</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>23885540.528094</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>18653763.1138731</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>14660300.000001</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>14750300.0000003</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>14869599.9999968</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>15009500.0000009</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>15254999.9999965</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>15504600.0000012</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>15872400.0000087</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>16265199.9999964</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>16511599.9999961</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>16604900.000005</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>17026199.9999995</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>17403499.9999922</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>17626200.0000013</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>17411600.0000046</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>17253999.9999982</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>17097099.9999994</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>17225300.0000013</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>17201300.0000072</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>16716568.3797774</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>16840985.3880799</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>17050165.7735219</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>17177475.2305278</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>17397748.2390644</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>18273534.46103</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>17824788.5729314</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>18296971.6907571</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>44239138748.0209</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>42277239999.999</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>41883316999.9999</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>42668851000.0019</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>43000463999.9966</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>43355111000.0039</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>43933947999.9914</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>44982249000.0018</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>41719221999.9942</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>46023216999.9928</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>46274049000.0006</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>46083018999.9993</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>46725658000.0113</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>47175487000.0046</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>45906790999.9975</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>44663348000.0014</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>44485909999.9937</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>44335814999.9857</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>43414699999.9994</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>41989161562.2158</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>41919035992.4415</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>42262970778.6776</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>42506737458.1</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>43062898006.7977</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>44490936433.3799</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>43708756362.2667</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>44236891369.6456</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>32965058780.2349</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>15256701999.9944</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>14869772999.9994</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>15366869000.0011</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>15468389999.9934</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>16111105000.0058</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>16412411999.9946</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>16907524999.9971</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>15749481999.9952</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>18018584999.993</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>17606360999.999</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>18786101000.0043</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>33100231000.0161</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>33466172000.0071</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>19689854999.9952</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>19558873999.9956</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>19384963999.9982</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>19582350999.989</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>19397415999.9869</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>30475362293.7934</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>30586541132.9788</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>30921886106.6731</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>31156588130.605</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>31482167069.4489</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>32850180392.2562</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>32037560455.9335</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>32735885606.9028</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1908019.38370154</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2181204.61964086</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2313739.36358511</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2378156.6326988</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2517103.46546794</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2769423.7677936</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2915993.9723354</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>3006233.24386309</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>3097301.23801257</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>3212910.07063285</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>3345839.78621777</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>3534811.12401302</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>3677352.66619573</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>3757313.16438583</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>3416077.06608966</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>3624624.2020844</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>3723779.81715512</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>3648372.1811873</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>3597517.30071774</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>3612458.54405885</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>3686005.18901625</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>3797761.42460763</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>3906905.940263</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>4029556.16245542</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>4050777.60813472</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>4096412.82742989</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>4122972.1401125</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>651649.271034766</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>750894.237085948</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>798278.36081248</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>792616.998208279</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>850609.504966515</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>898575.576185548</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>933860.986858833</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>966625.928730204</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>1007245.65502225</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>1038644.5210592</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>1067708.7566784</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>1111386.69629005</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>1152764.98763127</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>1155923.32439856</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1120451.33817705</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>1161386.29988015</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>1173696.47649374</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1155895.67317211</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>1144302.1948695</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>1186401.71342753</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>1209303.34228121</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>1206164.8051348</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>1275242.45411382</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>1276087.6049788</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>1317280.75836659</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>1296845.23871968</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>1331090.6893819</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3614,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3678,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4039,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
